--- a/file/测试用例.xlsx
+++ b/file/测试用例.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10500" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="登录" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
     <t>post</t>
   </si>
   <si>
-    <t>/api/auth/oauth2/token?username=admin&amp;randomStr=bbd162ca-e9de-4c7c-aebd-5aa01f173317&amp;code=9&amp;grant_type=password&amp;scope=server</t>
+    <t>/api/auth/b/verifycode/token</t>
   </si>
   <si>
     <t>data</t>
@@ -77,6 +77,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>{"sensitiveId":"","sensitiveWord":"</t>
     </r>
     <r>

--- a/file/测试用例.xlsx
+++ b/file/测试用例.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="登录" sheetId="1" r:id="rId1"/>
-    <sheet name="用例" sheetId="2" r:id="rId2"/>
+    <sheet name="不动产" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
   <si>
     <t>方法</t>
   </si>
@@ -61,66 +61,312 @@
     <t>ok</t>
   </si>
   <si>
-    <t>/api/admin/i18n</t>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>新增动态台账-资产</t>
+  </si>
+  <si>
+    <t>/api/assets/housing</t>
   </si>
   <si>
     <t>json</t>
   </si>
   <si>
-    <t>{"id":"","name":"router.moderDiagramView","zhCn":"小屏看板","en":"LittleBook"}</t>
-  </si>
-  <si>
-    <t>{"ok":"true"}</t>
-  </si>
-  <si>
-    <t>/api/admin/sysSensitiveWord</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>{"sensitiveId":"","sensitiveWord":"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>特殊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>","sensitiveType":"1","remark":"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这是一个敏感词</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>"}</t>
-    </r>
+    <r>
+      <t>{"projectBuildingName":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>远大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>海湾云锦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号楼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/8001","housingName":"1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号楼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8001","housingType":1,"housingSerial":"","housingIsDelegate":1,"ownerId":"4867680275843252227","housingAddress":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>四川省成都市双流区高新区锦韵路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>669</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","housingOldAddress":"","longitude":"104.083760","latitude":"30.540004","housingBipDTO":{"bipNo":""},"correlationId":"","remark":"","definedFieldValueList":[{"createName":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>汪茜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","createTime":"2026-04-27","enableStatus":1,"fieldName":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单选这是单选</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","fieldType":3,"fieldTypeDesc":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单选</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","functionType":4,"id":"4871415605384708099","isAdjust":0,"isEdit":1,"isMust":0,"isOperate":0,"isUse":1,"options":[{"fieldId":"4871415605384708099","id":"4871415605400437763","isUse":null,"name":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单选</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1","sort":1},{"fieldId":"4871415605384708099","id":"4871415605404632067","isUse":null,"name":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单选</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2","sort":2}],"point":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>请选择单选</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","remark":null,"size":null,"sort":1,"span":null,"unit":null,"fieldId":"4871415605384708099"}],"houseTypeCoveredArea":"","houseTypeJactetArea":"","houseTypePublicArea":"","houseTypePublicRatio":"","houseTypeUsageArea":"","houseTypeRealCalcArea":"","houseTypeRightArea":"","houseTypeLeaseArea":"","houseTypeUnLeaseArea":"","housingStructure":"","direction":"","buildingId":"4877132740249518083","housingHoldNo":"8001","projectId":"4877132739364519939","floorId":"4877132740345987075","unitId":"4877132740312432643"}</t>
+    </r>
+  </si>
+  <si>
+    <t>{"status": 200}</t>
   </si>
 </sst>
 </file>
@@ -133,7 +379,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,6 +390,11 @@
     <font>
       <sz val="9"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -624,148 +875,157 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1085,44 +1345,44 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="17.6666666666667" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.6666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.6666666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="44.7777777777778" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.3333333333333" style="2" customWidth="1"/>
+    <col min="1" max="1" width="17.6666666666667" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.7777777777778" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.6666666666667" style="3" customWidth="1"/>
+    <col min="4" max="4" width="44.7777777777778" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.3333333333333" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="3" customFormat="1" spans="1:5">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1136,65 +1396,55 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="4"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.3333333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="41.3333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.3333333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="56.2222222222222" style="1" customWidth="1"/>
-    <col min="5" max="5" width="33.4444444444444" style="1" customWidth="1"/>
+    <col min="1" max="1" width="33.8888888888889" customWidth="1"/>
+    <col min="2" max="2" width="14.3333333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="41.3333333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.3333333333333" style="2" customWidth="1"/>
+    <col min="5" max="5" width="56.2222222222222" style="2" customWidth="1"/>
+    <col min="6" max="6" width="33.4444444444444" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="E2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/file/测试用例.xlsx
+++ b/file/测试用例.xlsx
@@ -74,6 +74,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>{"projectBuildingName":"</t>
     </r>
     <r>
@@ -1017,19 +1023,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1373,13 +1379,13 @@
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
@@ -1437,13 +1443,13 @@
       <c r="C2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="6" t="s">
         <v>15</v>
       </c>
     </row>

--- a/file/测试用例.xlsx
+++ b/file/测试用例.xlsx
@@ -74,12 +74,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
       <t>{"projectBuildingName":"</t>
     </r>
     <r>

--- a/file/测试用例.xlsx
+++ b/file/测试用例.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10500" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="登录" sheetId="1" r:id="rId1"/>
-    <sheet name="用例" sheetId="2" r:id="rId2"/>
+    <sheet name="不动产" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
   <si>
     <t>方法</t>
   </si>
@@ -49,7 +49,7 @@
     <t>post</t>
   </si>
   <si>
-    <t>/api/auth/oauth2/token?username=admin&amp;randomStr=bbd162ca-e9de-4c7c-aebd-5aa01f173317&amp;code=9&amp;grant_type=password&amp;scope=server</t>
+    <t>/api/auth/b/verifycode/token</t>
   </si>
   <si>
     <t>data</t>
@@ -61,60 +61,312 @@
     <t>ok</t>
   </si>
   <si>
-    <t>/api/admin/i18n</t>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>新增动态台账-资产</t>
+  </si>
+  <si>
+    <t>/api/assets/housing</t>
   </si>
   <si>
     <t>json</t>
   </si>
   <si>
-    <t>{"id":"","name":"router.moderDiagramView","zhCn":"小屏看板","en":"LittleBook"}</t>
-  </si>
-  <si>
-    <t>{"ok":"true"}</t>
-  </si>
-  <si>
-    <t>/api/admin/sysSensitiveWord</t>
-  </si>
-  <si>
-    <r>
-      <t>{"sensitiveId":"","sensitiveWord":"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>特殊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>","sensitiveType":"1","remark":"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这是一个敏感词</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>"}</t>
-    </r>
+    <r>
+      <t>{"projectBuildingName":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>远大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>海湾云锦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号楼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/8001","housingName":"1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号楼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8001","housingType":1,"housingSerial":"","housingIsDelegate":1,"ownerId":"4867680275843252227","housingAddress":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>四川省成都市双流区高新区锦韵路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>669</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","housingOldAddress":"","longitude":"104.083760","latitude":"30.540004","housingBipDTO":{"bipNo":""},"correlationId":"","remark":"","definedFieldValueList":[{"createName":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>汪茜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","createTime":"2026-04-27","enableStatus":1,"fieldName":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单选这是单选</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","fieldType":3,"fieldTypeDesc":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单选</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","functionType":4,"id":"4871415605384708099","isAdjust":0,"isEdit":1,"isMust":0,"isOperate":0,"isUse":1,"options":[{"fieldId":"4871415605384708099","id":"4871415605400437763","isUse":null,"name":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单选</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1","sort":1},{"fieldId":"4871415605384708099","id":"4871415605404632067","isUse":null,"name":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单选</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2","sort":2}],"point":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>请选择单选</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF041E49"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","remark":null,"size":null,"sort":1,"span":null,"unit":null,"fieldId":"4871415605384708099"}],"houseTypeCoveredArea":"","houseTypeJactetArea":"","houseTypePublicArea":"","houseTypePublicRatio":"","houseTypeUsageArea":"","houseTypeRealCalcArea":"","houseTypeRightArea":"","houseTypeLeaseArea":"","houseTypeUnLeaseArea":"","housingStructure":"","direction":"","buildingId":"4877132740249518083","housingHoldNo":"8001","projectId":"4877132739364519939","floorId":"4877132740345987075","unitId":"4877132740312432643"}</t>
+    </r>
+  </si>
+  <si>
+    <t>{"status": 200}</t>
   </si>
 </sst>
 </file>
@@ -127,7 +379,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,6 +390,11 @@
     <font>
       <sz val="9"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -618,152 +875,161 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1079,44 +1345,44 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="17.6666666666667" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.6666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.6666666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="44.7777777777778" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.3333333333333" style="2" customWidth="1"/>
+    <col min="1" max="1" width="17.6666666666667" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.7777777777778" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.6666666666667" style="3" customWidth="1"/>
+    <col min="4" max="4" width="44.7777777777778" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.3333333333333" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="3" customFormat="1" spans="1:5">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1130,65 +1396,55 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="4"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.3333333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="41.3333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.3333333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="56.2222222222222" style="1" customWidth="1"/>
-    <col min="5" max="5" width="33.4444444444444" style="1" customWidth="1"/>
+    <col min="1" max="1" width="33.8888888888889" customWidth="1"/>
+    <col min="2" max="2" width="14.3333333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="41.3333333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.3333333333333" style="2" customWidth="1"/>
+    <col min="5" max="5" width="56.2222222222222" style="2" customWidth="1"/>
+    <col min="6" max="6" width="33.4444444444444" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="E2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="F2" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/file/测试用例.xlsx
+++ b/file/测试用例.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="10500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="登录" sheetId="1" r:id="rId1"/>
@@ -73,297 +73,7 @@
     <t>json</t>
   </si>
   <si>
-    <r>
-      <t>{"projectBuildingName":"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>远大</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>海湾云锦</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>号楼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>层</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/8001","housingName":"1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>号楼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>层</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>8001","housingType":1,"housingSerial":"","housingIsDelegate":1,"ownerId":"4867680275843252227","housingAddress":"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>四川省成都市双流区高新区锦韵路</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>669</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>号</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>","housingOldAddress":"","longitude":"104.083760","latitude":"30.540004","housingBipDTO":{"bipNo":""},"correlationId":"","remark":"","definedFieldValueList":[{"createName":"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>汪茜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>","createTime":"2026-04-27","enableStatus":1,"fieldName":"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单选这是单选</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>","fieldType":3,"fieldTypeDesc":"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单选</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>","functionType":4,"id":"4871415605384708099","isAdjust":0,"isEdit":1,"isMust":0,"isOperate":0,"isUse":1,"options":[{"fieldId":"4871415605384708099","id":"4871415605400437763","isUse":null,"name":"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单选</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1","sort":1},{"fieldId":"4871415605384708099","id":"4871415605404632067","isUse":null,"name":"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单选</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2","sort":2}],"point":"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>请选择单选</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF041E49"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>","remark":null,"size":null,"sort":1,"span":null,"unit":null,"fieldId":"4871415605384708099"}],"houseTypeCoveredArea":"","houseTypeJactetArea":"","houseTypePublicArea":"","houseTypePublicRatio":"","houseTypeUsageArea":"","houseTypeRealCalcArea":"","houseTypeRightArea":"","houseTypeLeaseArea":"","houseTypeUnLeaseArea":"","housingStructure":"","direction":"","buildingId":"4877132740249518083","housingHoldNo":"8001","projectId":"4877132739364519939","floorId":"4877132740345987075","unitId":"4877132740312432643"}</t>
-    </r>
+    <t>{"projectBuildingName":"远大·海湾云锦/1号楼/1单元/8层/8001","housingName":"1号楼1单元8层8001","housingType":1,"housingSerial":"","housingIsDelegate":1,"ownerId":"4867680275843252227","housingAddress":"四川省成都市双流区高新区锦韵路669号","housingOldAddress":"","longitude":"104.083760","latitude":"30.540004","housingBipDTO":{"bipNo":""},"correlationId":"","remark":"","definedFieldValueList":[{"createName":"汪茜","createTime":"2026-04-27","enableStatus":1,"fieldName":"单选这是单选","fieldType":3,"fieldTypeDesc":"单选","functionType":4,"id":"4871415605384708099","isAdjust":0,"isEdit":1,"isMust":0,"isOperate":0,"isUse":1,"options":[{"fieldId":"4871415605384708099","id":"4871415605400437763","isUse":null,"name":"单选1","sort":1},{"fieldId":"4871415605384708099","id":"4871415605404632067","isUse":null,"name":"单选2","sort":2}],"point":"请选择单选","remark":null,"size":null,"sort":1,"span":null,"unit":null,"fieldId":"4871415605384708099"}],"houseTypeCoveredArea":"","houseTypeJactetArea":"","houseTypePublicArea":"","houseTypePublicRatio":"","houseTypeUsageArea":"","houseTypeRealCalcArea":"","houseTypeRightArea":"","houseTypeLeaseArea":"","houseTypeUnLeaseArea":"","housingStructure":"","direction":"","buildingId":"4877132740249518083","housingHoldNo":"8001","projectId":"4877132739364519939","floorId":"4877132740345987075","unitId":"4877132740312432643"}</t>
   </si>
   <si>
     <t>{"status": 200}</t>
@@ -379,7 +89,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -547,12 +257,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF041E49"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1009,26 +713,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1346,9 +1050,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="17.6666666666667" style="3" customWidth="1"/>
-    <col min="2" max="2" width="25.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="2" width="25.7777777777778" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.6666666666667" style="3" customWidth="1"/>
-    <col min="4" max="4" width="44.7777777777778" style="2" customWidth="1"/>
+    <col min="4" max="4" width="44.7777777777778" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.3333333333333" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1396,15 +1100,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="33.8888888888889" customWidth="1"/>
-    <col min="2" max="2" width="14.3333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="41.3333333333333" style="2" customWidth="1"/>
-    <col min="4" max="4" width="14.3333333333333" style="2" customWidth="1"/>
-    <col min="5" max="5" width="56.2222222222222" style="2" customWidth="1"/>
-    <col min="6" max="6" width="33.4444444444444" style="2" customWidth="1"/>
+    <col min="1" max="1" width="33.8888888888889" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3333333333333" style="2" customWidth="1"/>
+    <col min="3" max="3" width="41.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.3333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="56.2222222222222" style="1" customWidth="1"/>
+    <col min="6" max="6" width="33.4444444444444" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1446,6 +1150,9 @@
       <c r="F2" s="6" t="s">
         <v>15</v>
       </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="E3" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
